--- a/world_info/scraper/StarRiverArts.xlsx
+++ b/world_info/scraper/StarRiverArts.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1305"/>
+  <dimension ref="A1:O1345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
@@ -67342,7 +67342,6 @@
       <c r="J1266" t="n">
         <v>0</v>
       </c>
-      <c r="K1266" t="inlineStr"/>
       <c r="L1266" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -67353,8 +67352,6 @@
           <t>3天</t>
         </is>
       </c>
-      <c r="N1266" t="inlineStr"/>
-      <c r="O1266" t="inlineStr"/>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
@@ -67397,7 +67394,6 @@
       <c r="J1267" t="n">
         <v>0</v>
       </c>
-      <c r="K1267" t="inlineStr"/>
       <c r="L1267" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -67408,8 +67404,6 @@
           <t>3天</t>
         </is>
       </c>
-      <c r="N1267" t="inlineStr"/>
-      <c r="O1267" t="inlineStr"/>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -67712,15 +67706,11 @@
       <c r="J1272" t="n">
         <v>0</v>
       </c>
-      <c r="K1272" t="inlineStr"/>
-      <c r="L1272" t="inlineStr"/>
       <c r="M1272" t="inlineStr">
         <is>
           <t>228天</t>
         </is>
       </c>
-      <c r="N1272" t="inlineStr"/>
-      <c r="O1272" t="inlineStr"/>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -67763,15 +67753,11 @@
       <c r="J1273" t="n">
         <v>0</v>
       </c>
-      <c r="K1273" t="inlineStr"/>
-      <c r="L1273" t="inlineStr"/>
       <c r="M1273" t="inlineStr">
         <is>
           <t>228天</t>
         </is>
       </c>
-      <c r="N1273" t="inlineStr"/>
-      <c r="O1273" t="inlineStr"/>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -67814,7 +67800,6 @@
       <c r="J1274" t="n">
         <v>0</v>
       </c>
-      <c r="K1274" t="inlineStr"/>
       <c r="L1274" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -67825,8 +67810,6 @@
           <t>232天</t>
         </is>
       </c>
-      <c r="N1274" t="inlineStr"/>
-      <c r="O1274" t="inlineStr"/>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
@@ -67869,7 +67852,6 @@
       <c r="J1275" t="n">
         <v>0</v>
       </c>
-      <c r="K1275" t="inlineStr"/>
       <c r="L1275" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -67880,8 +67862,6 @@
           <t>232天</t>
         </is>
       </c>
-      <c r="N1275" t="inlineStr"/>
-      <c r="O1275" t="inlineStr"/>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
@@ -68054,7 +68034,6 @@
       <c r="J1278" t="n">
         <v>3</v>
       </c>
-      <c r="K1278" t="inlineStr"/>
       <c r="L1278" t="inlineStr">
         <is>
           <t>1.61%</t>
@@ -68065,8 +68044,6 @@
           <t>259天</t>
         </is>
       </c>
-      <c r="N1278" t="inlineStr"/>
-      <c r="O1278" t="inlineStr"/>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
@@ -68109,7 +68086,6 @@
       <c r="J1279" t="n">
         <v>3</v>
       </c>
-      <c r="K1279" t="inlineStr"/>
       <c r="L1279" t="inlineStr">
         <is>
           <t>1.61%</t>
@@ -68120,8 +68096,6 @@
           <t>259天</t>
         </is>
       </c>
-      <c r="N1279" t="inlineStr"/>
-      <c r="O1279" t="inlineStr"/>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
@@ -68164,7 +68138,6 @@
       <c r="J1280" t="n">
         <v>0</v>
       </c>
-      <c r="K1280" t="inlineStr"/>
       <c r="L1280" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -68175,8 +68148,6 @@
           <t>266天</t>
         </is>
       </c>
-      <c r="N1280" t="inlineStr"/>
-      <c r="O1280" t="inlineStr"/>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
@@ -68219,7 +68190,6 @@
       <c r="J1281" t="n">
         <v>0</v>
       </c>
-      <c r="K1281" t="inlineStr"/>
       <c r="L1281" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -68230,8 +68200,6 @@
           <t>266天</t>
         </is>
       </c>
-      <c r="N1281" t="inlineStr"/>
-      <c r="O1281" t="inlineStr"/>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
@@ -68274,7 +68242,6 @@
       <c r="J1282" t="n">
         <v>3</v>
       </c>
-      <c r="K1282" t="inlineStr"/>
       <c r="L1282" t="inlineStr">
         <is>
           <t>2.9%</t>
@@ -68285,8 +68252,6 @@
           <t>269天</t>
         </is>
       </c>
-      <c r="N1282" t="inlineStr"/>
-      <c r="O1282" t="inlineStr"/>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -68329,7 +68294,6 @@
       <c r="J1283" t="n">
         <v>3</v>
       </c>
-      <c r="K1283" t="inlineStr"/>
       <c r="L1283" t="inlineStr">
         <is>
           <t>2.9%</t>
@@ -68340,8 +68304,6 @@
           <t>269天</t>
         </is>
       </c>
-      <c r="N1283" t="inlineStr"/>
-      <c r="O1283" t="inlineStr"/>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
@@ -68514,7 +68476,6 @@
       <c r="J1286" t="n">
         <v>3</v>
       </c>
-      <c r="K1286" t="inlineStr"/>
       <c r="L1286" t="inlineStr">
         <is>
           <t>1.27%</t>
@@ -68525,8 +68486,6 @@
           <t>316天</t>
         </is>
       </c>
-      <c r="N1286" t="inlineStr"/>
-      <c r="O1286" t="inlineStr"/>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
@@ -68569,7 +68528,6 @@
       <c r="J1287" t="n">
         <v>3</v>
       </c>
-      <c r="K1287" t="inlineStr"/>
       <c r="L1287" t="inlineStr">
         <is>
           <t>1.27%</t>
@@ -68580,8 +68538,6 @@
           <t>316天</t>
         </is>
       </c>
-      <c r="N1287" t="inlineStr"/>
-      <c r="O1287" t="inlineStr"/>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
@@ -68884,7 +68840,6 @@
       <c r="J1292" t="n">
         <v>0</v>
       </c>
-      <c r="K1292" t="inlineStr"/>
       <c r="L1292" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -68895,8 +68850,6 @@
           <t>490天</t>
         </is>
       </c>
-      <c r="N1292" t="inlineStr"/>
-      <c r="O1292" t="inlineStr"/>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
@@ -68939,7 +68892,6 @@
       <c r="J1293" t="n">
         <v>0</v>
       </c>
-      <c r="K1293" t="inlineStr"/>
       <c r="L1293" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -68950,8 +68902,6 @@
           <t>490天</t>
         </is>
       </c>
-      <c r="N1293" t="inlineStr"/>
-      <c r="O1293" t="inlineStr"/>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
@@ -68994,7 +68944,6 @@
       <c r="J1294" t="n">
         <v>4</v>
       </c>
-      <c r="K1294" t="inlineStr"/>
       <c r="L1294" t="inlineStr">
         <is>
           <t>1.5%</t>
@@ -69005,8 +68954,6 @@
           <t>560天</t>
         </is>
       </c>
-      <c r="N1294" t="inlineStr"/>
-      <c r="O1294" t="inlineStr"/>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -69049,7 +68996,6 @@
       <c r="J1295" t="n">
         <v>4</v>
       </c>
-      <c r="K1295" t="inlineStr"/>
       <c r="L1295" t="inlineStr">
         <is>
           <t>1.5%</t>
@@ -69060,8 +69006,6 @@
           <t>560天</t>
         </is>
       </c>
-      <c r="N1295" t="inlineStr"/>
-      <c r="O1295" t="inlineStr"/>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -69234,7 +69178,6 @@
       <c r="J1298" t="n">
         <v>0</v>
       </c>
-      <c r="K1298" t="inlineStr"/>
       <c r="L1298" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69245,8 +69188,6 @@
           <t>626天</t>
         </is>
       </c>
-      <c r="N1298" t="inlineStr"/>
-      <c r="O1298" t="inlineStr"/>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
@@ -69289,7 +69230,6 @@
       <c r="J1299" t="n">
         <v>0</v>
       </c>
-      <c r="K1299" t="inlineStr"/>
       <c r="L1299" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69300,8 +69240,6 @@
           <t>626天</t>
         </is>
       </c>
-      <c r="N1299" t="inlineStr"/>
-      <c r="O1299" t="inlineStr"/>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
@@ -69474,7 +69412,6 @@
       <c r="J1302" t="n">
         <v>0</v>
       </c>
-      <c r="K1302" t="inlineStr"/>
       <c r="L1302" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69485,8 +69422,6 @@
           <t>663天</t>
         </is>
       </c>
-      <c r="N1302" t="inlineStr"/>
-      <c r="O1302" t="inlineStr"/>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
@@ -69529,7 +69464,6 @@
       <c r="J1303" t="n">
         <v>0</v>
       </c>
-      <c r="K1303" t="inlineStr"/>
       <c r="L1303" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69540,8 +69474,6 @@
           <t>663天</t>
         </is>
       </c>
-      <c r="N1303" t="inlineStr"/>
-      <c r="O1303" t="inlineStr"/>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -69584,7 +69516,6 @@
       <c r="J1304" t="n">
         <v>0</v>
       </c>
-      <c r="K1304" t="inlineStr"/>
       <c r="L1304" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69595,8 +69526,6 @@
           <t>841天</t>
         </is>
       </c>
-      <c r="N1304" t="inlineStr"/>
-      <c r="O1304" t="inlineStr"/>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -69639,7 +69568,6 @@
       <c r="J1305" t="n">
         <v>0</v>
       </c>
-      <c r="K1305" t="inlineStr"/>
       <c r="L1305" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69650,8 +69578,2358 @@
           <t>841天</t>
         </is>
       </c>
-      <c r="N1305" t="inlineStr"/>
-      <c r="O1305" t="inlineStr"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Beyond Gravity ˸ An Interplanetary Travel Showcase</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>wrld_660d90dd-2a8e-4743-9b70-1c6237f8192b</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:25:35.598Z</t>
+        </is>
+      </c>
+      <c r="F1306" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1306" t="inlineStr"/>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1306" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="N1306" t="inlineStr"/>
+      <c r="O1306" t="inlineStr"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Beyond Gravity ˸ An Interplanetary Travel Showcase</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>wrld_660d90dd-2a8e-4743-9b70-1c6237f8192b</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:25:35.598Z</t>
+        </is>
+      </c>
+      <c r="F1307" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1307" t="inlineStr"/>
+      <c r="L1307" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1307" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="N1307" t="inlineStr"/>
+      <c r="O1307" t="inlineStr"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>SpeedStar Paradise （StarSight Mt․觀星山 CVS2）</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>wrld_c0f03f3e-ca4c-48cb-8aea-14ed13c1ee03</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>2025-11-17T14:03:16.240Z</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>2026-02-21T14:40:32.411Z</t>
+        </is>
+      </c>
+      <c r="F1308" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>46</v>
+      </c>
+      <c r="I1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1308" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1308" t="inlineStr">
+        <is>
+          <t>4天</t>
+        </is>
+      </c>
+      <c r="L1308" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="M1308" t="inlineStr">
+        <is>
+          <t>41天</t>
+        </is>
+      </c>
+      <c r="N1308" t="inlineStr">
+        <is>
+          <t>137天</t>
+        </is>
+      </c>
+      <c r="O1308" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>SpeedStar Paradise （StarSight Mt․觀星山 CVS2）</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>wrld_c0f03f3e-ca4c-48cb-8aea-14ed13c1ee03</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>2025-11-17T14:03:16.240Z</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>2026-02-21T14:40:32.411Z</t>
+        </is>
+      </c>
+      <c r="F1309" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>46</v>
+      </c>
+      <c r="I1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1309" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1309" t="inlineStr">
+        <is>
+          <t>4天</t>
+        </is>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="M1309" t="inlineStr">
+        <is>
+          <t>41天</t>
+        </is>
+      </c>
+      <c r="N1309" t="inlineStr">
+        <is>
+          <t>137天</t>
+        </is>
+      </c>
+      <c r="O1309" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Project Origin v1․0 Hangout and chill ǃ （Minecraft Build Project）</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>wrld_fb9540f8-68f1-42e8-9430-558fc2d568c4</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>2023-10-15T12:21:09.717Z</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>2025-11-12T15:28:46.998Z</t>
+        </is>
+      </c>
+      <c r="F1310" t="n">
+        <v>4807</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>189</v>
+      </c>
+      <c r="I1310" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1310" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1310" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="M1310" t="inlineStr">
+        <is>
+          <t>142天</t>
+        </is>
+      </c>
+      <c r="N1310" t="inlineStr">
+        <is>
+          <t>901天</t>
+        </is>
+      </c>
+      <c r="O1310" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Project Origin v1․0 Hangout and chill ǃ （Minecraft Build Project）</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>wrld_fb9540f8-68f1-42e8-9430-558fc2d568c4</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>2023-10-15T12:21:09.717Z</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>2025-11-12T15:28:46.998Z</t>
+        </is>
+      </c>
+      <c r="F1311" t="n">
+        <v>4807</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>189</v>
+      </c>
+      <c r="I1311" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1311" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1311" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="M1311" t="inlineStr">
+        <is>
+          <t>142天</t>
+        </is>
+      </c>
+      <c r="N1311" t="inlineStr">
+        <is>
+          <t>901天</t>
+        </is>
+      </c>
+      <c r="O1311" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Starsight Museum</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>wrld_befc82b9-48d1-4d2a-8269-fb1ac1518f69</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>2025-08-13T13:48:58.458Z</t>
+        </is>
+      </c>
+      <c r="F1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1312" t="inlineStr"/>
+      <c r="L1312" t="inlineStr"/>
+      <c r="M1312" t="inlineStr">
+        <is>
+          <t>233天</t>
+        </is>
+      </c>
+      <c r="N1312" t="inlineStr"/>
+      <c r="O1312" t="inlineStr"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Starsight Museum</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>wrld_befc82b9-48d1-4d2a-8269-fb1ac1518f69</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>2025-08-13T13:48:58.458Z</t>
+        </is>
+      </c>
+      <c r="F1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1313" t="inlineStr"/>
+      <c r="L1313" t="inlineStr"/>
+      <c r="M1313" t="inlineStr">
+        <is>
+          <t>233天</t>
+        </is>
+      </c>
+      <c r="N1313" t="inlineStr"/>
+      <c r="O1313" t="inlineStr"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>wrld_44e2cf46-b090-4c70-b5ba-9f7e7ec89d4f</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>2025-08-09T16:53:49.952Z</t>
+        </is>
+      </c>
+      <c r="F1314" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1314" t="inlineStr"/>
+      <c r="L1314" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1314" t="inlineStr">
+        <is>
+          <t>236天</t>
+        </is>
+      </c>
+      <c r="N1314" t="inlineStr"/>
+      <c r="O1314" t="inlineStr"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>wrld_44e2cf46-b090-4c70-b5ba-9f7e7ec89d4f</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>2025-08-09T16:53:49.952Z</t>
+        </is>
+      </c>
+      <c r="F1315" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1315" t="inlineStr"/>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1315" t="inlineStr">
+        <is>
+          <t>236天</t>
+        </is>
+      </c>
+      <c r="N1315" t="inlineStr"/>
+      <c r="O1315" t="inlineStr"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge CVS2 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>wrld_c4d985d3-11de-4a89-9e8b-60b0342a1676</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>2025-05-03T22:35:59.524Z</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>2025-08-02T09:39:48.354Z</t>
+        </is>
+      </c>
+      <c r="F1316" t="n">
+        <v>3578</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>146</v>
+      </c>
+      <c r="I1316" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1316" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1316" t="inlineStr">
+        <is>
+          <t>12天</t>
+        </is>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+      <c r="M1316" t="inlineStr">
+        <is>
+          <t>244天</t>
+        </is>
+      </c>
+      <c r="N1316" t="inlineStr">
+        <is>
+          <t>334天</t>
+        </is>
+      </c>
+      <c r="O1316" t="n">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge CVS2 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>wrld_c4d985d3-11de-4a89-9e8b-60b0342a1676</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>2025-05-03T22:35:59.524Z</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>2025-08-02T09:39:48.354Z</t>
+        </is>
+      </c>
+      <c r="F1317" t="n">
+        <v>3578</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>146</v>
+      </c>
+      <c r="I1317" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1317" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1317" t="inlineStr">
+        <is>
+          <t>12天</t>
+        </is>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+      <c r="M1317" t="inlineStr">
+        <is>
+          <t>244天</t>
+        </is>
+      </c>
+      <c r="N1317" t="inlineStr">
+        <is>
+          <t>334天</t>
+        </is>
+      </c>
+      <c r="O1317" t="n">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>StarRiver Space Program v0․1․1 LiftOff</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>wrld_f3acb654-f2ab-49aa-9108-d261c53c5d64</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>2025-07-13T11:38:02.242Z</t>
+        </is>
+      </c>
+      <c r="F1318" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1318" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1318" t="inlineStr"/>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="M1318" t="inlineStr">
+        <is>
+          <t>264天</t>
+        </is>
+      </c>
+      <c r="N1318" t="inlineStr"/>
+      <c r="O1318" t="inlineStr"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>StarRiver Space Program v0․1․1 LiftOff</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>wrld_f3acb654-f2ab-49aa-9108-d261c53c5d64</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>2025-07-13T11:38:02.242Z</t>
+        </is>
+      </c>
+      <c r="F1319" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1319" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1319" t="inlineStr"/>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="M1319" t="inlineStr">
+        <is>
+          <t>264天</t>
+        </is>
+      </c>
+      <c r="N1319" t="inlineStr"/>
+      <c r="O1319" t="inlineStr"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T SunMoonLake 日月潭 南投山道</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>wrld_1b189721-fa5d-4c64-a24b-9a2c5b89b3b5</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>2025-07-06T07:24:59.566Z</t>
+        </is>
+      </c>
+      <c r="F1320" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1320" t="inlineStr"/>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1320" t="inlineStr">
+        <is>
+          <t>271天</t>
+        </is>
+      </c>
+      <c r="N1320" t="inlineStr"/>
+      <c r="O1320" t="inlineStr"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T SunMoonLake 日月潭 南投山道</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>wrld_1b189721-fa5d-4c64-a24b-9a2c5b89b3b5</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>2025-07-06T07:24:59.566Z</t>
+        </is>
+      </c>
+      <c r="F1321" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1321" t="inlineStr"/>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1321" t="inlineStr">
+        <is>
+          <t>271天</t>
+        </is>
+      </c>
+      <c r="N1321" t="inlineStr"/>
+      <c r="O1321" t="inlineStr"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T WuLing 武嶺（佐久間峠） 合歡山山道</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>wrld_5fb84156-598a-43c8-8a2b-2c9aa7c95b40</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>2025-07-03T13:07:32.404Z</t>
+        </is>
+      </c>
+      <c r="F1322" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1322" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1322" t="inlineStr"/>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="M1322" t="inlineStr">
+        <is>
+          <t>274天</t>
+        </is>
+      </c>
+      <c r="N1322" t="inlineStr"/>
+      <c r="O1322" t="inlineStr"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T WuLing 武嶺（佐久間峠） 合歡山山道</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>wrld_5fb84156-598a-43c8-8a2b-2c9aa7c95b40</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>2025-07-03T13:07:32.404Z</t>
+        </is>
+      </c>
+      <c r="F1323" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1323" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1323" t="inlineStr"/>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="M1323" t="inlineStr">
+        <is>
+          <t>274天</t>
+        </is>
+      </c>
+      <c r="N1323" t="inlineStr"/>
+      <c r="O1323" t="inlineStr"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge Sacc 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>wrld_a6f9cdae-d393-4572-b019-015e4ec6eb35</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>2025-04-09T11:56:42.006Z</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>2025-05-27T15:40:33.056Z</t>
+        </is>
+      </c>
+      <c r="F1324" t="n">
+        <v>915</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>72</v>
+      </c>
+      <c r="I1324" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1324" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1324" t="inlineStr">
+        <is>
+          <t>15天</t>
+        </is>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>7.87%</t>
+        </is>
+      </c>
+      <c r="M1324" t="inlineStr">
+        <is>
+          <t>310天</t>
+        </is>
+      </c>
+      <c r="N1324" t="inlineStr">
+        <is>
+          <t>359天</t>
+        </is>
+      </c>
+      <c r="O1324" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge Sacc 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>wrld_a6f9cdae-d393-4572-b019-015e4ec6eb35</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>2025-04-09T11:56:42.006Z</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>2025-05-27T15:40:33.056Z</t>
+        </is>
+      </c>
+      <c r="F1325" t="n">
+        <v>915</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>72</v>
+      </c>
+      <c r="I1325" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1325" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1325" t="inlineStr">
+        <is>
+          <t>15天</t>
+        </is>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>7.87%</t>
+        </is>
+      </c>
+      <c r="M1325" t="inlineStr">
+        <is>
+          <t>310天</t>
+        </is>
+      </c>
+      <c r="N1325" t="inlineStr">
+        <is>
+          <t>359天</t>
+        </is>
+      </c>
+      <c r="O1325" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>日月潭外周道 Sun Moon Lake</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>wrld_6e465490-9b15-4d2b-b4fe-1ea06e09e55a</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>2025-05-17T13:55:05.489Z</t>
+        </is>
+      </c>
+      <c r="F1326" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1326" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1326" t="inlineStr"/>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="M1326" t="inlineStr">
+        <is>
+          <t>321天</t>
+        </is>
+      </c>
+      <c r="N1326" t="inlineStr"/>
+      <c r="O1326" t="inlineStr"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>日月潭外周道 Sun Moon Lake</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>wrld_6e465490-9b15-4d2b-b4fe-1ea06e09e55a</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>2025-05-17T13:55:05.489Z</t>
+        </is>
+      </c>
+      <c r="F1327" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1327" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1327" t="inlineStr"/>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="M1327" t="inlineStr">
+        <is>
+          <t>321天</t>
+        </is>
+      </c>
+      <c r="N1327" t="inlineStr"/>
+      <c r="O1327" t="inlineStr"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>星門廣場StarGATE Exhibition</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>wrld_16498412-b9e0-404c-9da7-114484c89ecd</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>2024-07-22T05:06:07.749Z</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>2025-05-08T16:46:38.069Z</t>
+        </is>
+      </c>
+      <c r="F1328" t="n">
+        <v>823</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1328" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1328" t="inlineStr">
+        <is>
+          <t>24天</t>
+        </is>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="M1328" t="inlineStr">
+        <is>
+          <t>329天</t>
+        </is>
+      </c>
+      <c r="N1328" t="inlineStr">
+        <is>
+          <t>620天</t>
+        </is>
+      </c>
+      <c r="O1328" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>星門廣場StarGATE Exhibition</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>wrld_16498412-b9e0-404c-9da7-114484c89ecd</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>2024-07-22T05:06:07.749Z</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>2025-05-08T16:46:38.069Z</t>
+        </is>
+      </c>
+      <c r="F1329" t="n">
+        <v>823</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1329" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1329" t="inlineStr">
+        <is>
+          <t>24天</t>
+        </is>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="M1329" t="inlineStr">
+        <is>
+          <t>329天</t>
+        </is>
+      </c>
+      <c r="N1329" t="inlineStr">
+        <is>
+          <t>620天</t>
+        </is>
+      </c>
+      <c r="O1329" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Iseri Nina's Room （Girls Band Cry）</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>wrld_014b19d4-10fc-448d-aaf4-100067cc8eb2</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>2025-12-15T07:34:25.776Z</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>2025-04-10T13:03:37.715Z</t>
+        </is>
+      </c>
+      <c r="F1330" t="n">
+        <v>503</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>69</v>
+      </c>
+      <c r="I1330" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1330" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1330" t="inlineStr">
+        <is>
+          <t>258天</t>
+        </is>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>13.72%</t>
+        </is>
+      </c>
+      <c r="M1330" t="inlineStr">
+        <is>
+          <t>358天</t>
+        </is>
+      </c>
+      <c r="N1330" t="inlineStr">
+        <is>
+          <t>109天</t>
+        </is>
+      </c>
+      <c r="O1330" t="n">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Iseri Nina's Room （Girls Band Cry）</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>wrld_014b19d4-10fc-448d-aaf4-100067cc8eb2</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>2025-12-15T07:34:25.776Z</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>2025-04-10T13:03:37.715Z</t>
+        </is>
+      </c>
+      <c r="F1331" t="n">
+        <v>503</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>69</v>
+      </c>
+      <c r="I1331" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1331" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1331" t="inlineStr">
+        <is>
+          <t>258天</t>
+        </is>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t>13.72%</t>
+        </is>
+      </c>
+      <c r="M1331" t="inlineStr">
+        <is>
+          <t>358天</t>
+        </is>
+      </c>
+      <c r="N1331" t="inlineStr">
+        <is>
+          <t>109天</t>
+        </is>
+      </c>
+      <c r="O1331" t="n">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Metro Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>wrld_39eab7ef-be49-4bb2-bb63-56bc30200b82</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>2024-11-24T13:59:30.261Z</t>
+        </is>
+      </c>
+      <c r="F1332" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1332" t="inlineStr"/>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1332" t="inlineStr">
+        <is>
+          <t>495天</t>
+        </is>
+      </c>
+      <c r="N1332" t="inlineStr"/>
+      <c r="O1332" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Metro Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>wrld_39eab7ef-be49-4bb2-bb63-56bc30200b82</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>2024-11-24T13:59:30.261Z</t>
+        </is>
+      </c>
+      <c r="F1333" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1333" t="inlineStr"/>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1333" t="inlineStr">
+        <is>
+          <t>495天</t>
+        </is>
+      </c>
+      <c r="N1333" t="inlineStr"/>
+      <c r="O1333" t="inlineStr"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Taipei MRT 大坪林站 by StarRiver（未完成）</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>wrld_b7193f7d-4616-4b3e-8236-e2f4c7da2d8d</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>2024-09-15T05:18:23.226Z</t>
+        </is>
+      </c>
+      <c r="F1334" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1334" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1334" t="inlineStr"/>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="M1334" t="inlineStr">
+        <is>
+          <t>565天</t>
+        </is>
+      </c>
+      <c r="N1334" t="inlineStr"/>
+      <c r="O1334" t="inlineStr"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Taipei MRT 大坪林站 by StarRiver（未完成）</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>wrld_b7193f7d-4616-4b3e-8236-e2f4c7da2d8d</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>2024-09-15T05:18:23.226Z</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1335" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1335" t="inlineStr"/>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="M1335" t="inlineStr">
+        <is>
+          <t>565天</t>
+        </is>
+      </c>
+      <c r="N1335" t="inlineStr"/>
+      <c r="O1335" t="inlineStr"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Free Trajectory -A Landscape Recreation Experience</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>wrld_81e98a0f-b8eb-4a9b-b01b-35d26758c41c</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>2024-07-23T14:43:36.014Z</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>2024-07-22T19:52:03.599Z</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v>373</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1336" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1336" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="M1336" t="inlineStr">
+        <is>
+          <t>619天</t>
+        </is>
+      </c>
+      <c r="N1336" t="inlineStr">
+        <is>
+          <t>619天</t>
+        </is>
+      </c>
+      <c r="O1336" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Free Trajectory -A Landscape Recreation Experience</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>wrld_81e98a0f-b8eb-4a9b-b01b-35d26758c41c</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>2024-07-23T14:43:36.014Z</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>2024-07-22T19:52:03.599Z</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v>373</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1337" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1337" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="L1337" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="M1337" t="inlineStr">
+        <is>
+          <t>619天</t>
+        </is>
+      </c>
+      <c r="N1337" t="inlineStr">
+        <is>
+          <t>619天</t>
+        </is>
+      </c>
+      <c r="O1337" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Project：Hide＆Seek LAB（UNFINISHED ）</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>wrld_bac386e9-a543-48e7-a12d-fe9bd3521493</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>2024-07-11T09:44:06.067Z</t>
+        </is>
+      </c>
+      <c r="F1338" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1338" t="inlineStr"/>
+      <c r="L1338" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1338" t="inlineStr">
+        <is>
+          <t>631天</t>
+        </is>
+      </c>
+      <c r="N1338" t="inlineStr"/>
+      <c r="O1338" t="inlineStr"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Project：Hide＆Seek LAB（UNFINISHED ）</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>wrld_bac386e9-a543-48e7-a12d-fe9bd3521493</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>2024-07-11T09:44:06.067Z</t>
+        </is>
+      </c>
+      <c r="F1339" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1339" t="inlineStr"/>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1339" t="inlineStr">
+        <is>
+          <t>631天</t>
+        </is>
+      </c>
+      <c r="N1339" t="inlineStr"/>
+      <c r="O1339" t="inlineStr"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Simple Green Room（Quest 3 MR）</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>wrld_14e668e2-f41b-4655-9440-51be3be0ae81</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>2024-07-08T21:05:28.545Z</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>2024-07-11T08:38:23.384Z</t>
+        </is>
+      </c>
+      <c r="F1340" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1340" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1340" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1340" t="inlineStr">
+        <is>
+          <t>263天</t>
+        </is>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="M1340" t="inlineStr">
+        <is>
+          <t>631天</t>
+        </is>
+      </c>
+      <c r="N1340" t="inlineStr">
+        <is>
+          <t>633天</t>
+        </is>
+      </c>
+      <c r="O1340" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Simple Green Room（Quest 3 MR）</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>wrld_14e668e2-f41b-4655-9440-51be3be0ae81</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>2024-07-08T21:05:28.545Z</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>2024-07-11T08:38:23.384Z</t>
+        </is>
+      </c>
+      <c r="F1341" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1341" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1341" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1341" t="inlineStr">
+        <is>
+          <t>263天</t>
+        </is>
+      </c>
+      <c r="L1341" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="M1341" t="inlineStr">
+        <is>
+          <t>631天</t>
+        </is>
+      </c>
+      <c r="N1341" t="inlineStr">
+        <is>
+          <t>633天</t>
+        </is>
+      </c>
+      <c r="O1341" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Ruined斷垣殘壁 （測試）</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>wrld_7d7a9a66-df6a-4e2c-96fb-19b4dc53c430</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>2024-06-04T16:33:51.575Z</t>
+        </is>
+      </c>
+      <c r="F1342" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1342" t="inlineStr"/>
+      <c r="L1342" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1342" t="inlineStr">
+        <is>
+          <t>667天</t>
+        </is>
+      </c>
+      <c r="N1342" t="inlineStr"/>
+      <c r="O1342" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Ruined斷垣殘壁 （測試）</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>wrld_7d7a9a66-df6a-4e2c-96fb-19b4dc53c430</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>2024-06-04T16:33:51.575Z</t>
+        </is>
+      </c>
+      <c r="F1343" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1343" t="inlineStr"/>
+      <c r="L1343" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1343" t="inlineStr">
+        <is>
+          <t>667天</t>
+        </is>
+      </c>
+      <c r="N1343" t="inlineStr"/>
+      <c r="O1343" t="inlineStr"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Project˸ Taiwan</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>wrld_2e5e73d8-758f-4e2d-87db-7770762d52f0</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>2023-12-08T22:31:41.588Z</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1344" t="inlineStr"/>
+      <c r="L1344" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1344" t="inlineStr">
+        <is>
+          <t>846天</t>
+        </is>
+      </c>
+      <c r="N1344" t="inlineStr"/>
+      <c r="O1344" t="inlineStr"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Project˸ Taiwan</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>wrld_2e5e73d8-758f-4e2d-87db-7770762d52f0</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>2023-12-08T22:31:41.588Z</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1345" t="inlineStr"/>
+      <c r="L1345" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1345" t="inlineStr">
+        <is>
+          <t>846天</t>
+        </is>
+      </c>
+      <c r="N1345" t="inlineStr"/>
+      <c r="O1345" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O655">

--- a/world_info/scraper/StarRiverArts.xlsx
+++ b/world_info/scraper/StarRiverArts.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1345"/>
+  <dimension ref="A1:O1385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
@@ -69620,7 +69620,6 @@
       <c r="J1306" t="n">
         <v>0</v>
       </c>
-      <c r="K1306" t="inlineStr"/>
       <c r="L1306" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69631,8 +69630,6 @@
           <t>0天</t>
         </is>
       </c>
-      <c r="N1306" t="inlineStr"/>
-      <c r="O1306" t="inlineStr"/>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
@@ -69675,7 +69672,6 @@
       <c r="J1307" t="n">
         <v>0</v>
       </c>
-      <c r="K1307" t="inlineStr"/>
       <c r="L1307" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -69686,8 +69682,6 @@
           <t>0天</t>
         </is>
       </c>
-      <c r="N1307" t="inlineStr"/>
-      <c r="O1307" t="inlineStr"/>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -69990,15 +69984,11 @@
       <c r="J1312" t="n">
         <v>0</v>
       </c>
-      <c r="K1312" t="inlineStr"/>
-      <c r="L1312" t="inlineStr"/>
       <c r="M1312" t="inlineStr">
         <is>
           <t>233天</t>
         </is>
       </c>
-      <c r="N1312" t="inlineStr"/>
-      <c r="O1312" t="inlineStr"/>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
@@ -70041,15 +70031,11 @@
       <c r="J1313" t="n">
         <v>0</v>
       </c>
-      <c r="K1313" t="inlineStr"/>
-      <c r="L1313" t="inlineStr"/>
       <c r="M1313" t="inlineStr">
         <is>
           <t>233天</t>
         </is>
       </c>
-      <c r="N1313" t="inlineStr"/>
-      <c r="O1313" t="inlineStr"/>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
@@ -70092,7 +70078,6 @@
       <c r="J1314" t="n">
         <v>0</v>
       </c>
-      <c r="K1314" t="inlineStr"/>
       <c r="L1314" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -70103,8 +70088,6 @@
           <t>236天</t>
         </is>
       </c>
-      <c r="N1314" t="inlineStr"/>
-      <c r="O1314" t="inlineStr"/>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
@@ -70147,7 +70130,6 @@
       <c r="J1315" t="n">
         <v>0</v>
       </c>
-      <c r="K1315" t="inlineStr"/>
       <c r="L1315" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -70158,8 +70140,6 @@
           <t>236天</t>
         </is>
       </c>
-      <c r="N1315" t="inlineStr"/>
-      <c r="O1315" t="inlineStr"/>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
@@ -70332,7 +70312,6 @@
       <c r="J1318" t="n">
         <v>3</v>
       </c>
-      <c r="K1318" t="inlineStr"/>
       <c r="L1318" t="inlineStr">
         <is>
           <t>1.61%</t>
@@ -70343,8 +70322,6 @@
           <t>264天</t>
         </is>
       </c>
-      <c r="N1318" t="inlineStr"/>
-      <c r="O1318" t="inlineStr"/>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
@@ -70387,7 +70364,6 @@
       <c r="J1319" t="n">
         <v>3</v>
       </c>
-      <c r="K1319" t="inlineStr"/>
       <c r="L1319" t="inlineStr">
         <is>
           <t>1.61%</t>
@@ -70398,8 +70374,6 @@
           <t>264天</t>
         </is>
       </c>
-      <c r="N1319" t="inlineStr"/>
-      <c r="O1319" t="inlineStr"/>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
@@ -70442,7 +70416,6 @@
       <c r="J1320" t="n">
         <v>0</v>
       </c>
-      <c r="K1320" t="inlineStr"/>
       <c r="L1320" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -70453,8 +70426,6 @@
           <t>271天</t>
         </is>
       </c>
-      <c r="N1320" t="inlineStr"/>
-      <c r="O1320" t="inlineStr"/>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
@@ -70497,7 +70468,6 @@
       <c r="J1321" t="n">
         <v>0</v>
       </c>
-      <c r="K1321" t="inlineStr"/>
       <c r="L1321" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -70508,8 +70478,6 @@
           <t>271天</t>
         </is>
       </c>
-      <c r="N1321" t="inlineStr"/>
-      <c r="O1321" t="inlineStr"/>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
@@ -70552,7 +70520,6 @@
       <c r="J1322" t="n">
         <v>3</v>
       </c>
-      <c r="K1322" t="inlineStr"/>
       <c r="L1322" t="inlineStr">
         <is>
           <t>2.9%</t>
@@ -70563,8 +70530,6 @@
           <t>274天</t>
         </is>
       </c>
-      <c r="N1322" t="inlineStr"/>
-      <c r="O1322" t="inlineStr"/>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
@@ -70607,7 +70572,6 @@
       <c r="J1323" t="n">
         <v>3</v>
       </c>
-      <c r="K1323" t="inlineStr"/>
       <c r="L1323" t="inlineStr">
         <is>
           <t>2.9%</t>
@@ -70618,8 +70582,6 @@
           <t>274天</t>
         </is>
       </c>
-      <c r="N1323" t="inlineStr"/>
-      <c r="O1323" t="inlineStr"/>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
@@ -70792,7 +70754,6 @@
       <c r="J1326" t="n">
         <v>3</v>
       </c>
-      <c r="K1326" t="inlineStr"/>
       <c r="L1326" t="inlineStr">
         <is>
           <t>1.27%</t>
@@ -70803,8 +70764,6 @@
           <t>321天</t>
         </is>
       </c>
-      <c r="N1326" t="inlineStr"/>
-      <c r="O1326" t="inlineStr"/>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
@@ -70847,7 +70806,6 @@
       <c r="J1327" t="n">
         <v>3</v>
       </c>
-      <c r="K1327" t="inlineStr"/>
       <c r="L1327" t="inlineStr">
         <is>
           <t>1.27%</t>
@@ -70858,8 +70816,6 @@
           <t>321天</t>
         </is>
       </c>
-      <c r="N1327" t="inlineStr"/>
-      <c r="O1327" t="inlineStr"/>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
@@ -71162,7 +71118,6 @@
       <c r="J1332" t="n">
         <v>0</v>
       </c>
-      <c r="K1332" t="inlineStr"/>
       <c r="L1332" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71173,8 +71128,6 @@
           <t>495天</t>
         </is>
       </c>
-      <c r="N1332" t="inlineStr"/>
-      <c r="O1332" t="inlineStr"/>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
@@ -71217,7 +71170,6 @@
       <c r="J1333" t="n">
         <v>0</v>
       </c>
-      <c r="K1333" t="inlineStr"/>
       <c r="L1333" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71228,8 +71180,6 @@
           <t>495天</t>
         </is>
       </c>
-      <c r="N1333" t="inlineStr"/>
-      <c r="O1333" t="inlineStr"/>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
@@ -71272,7 +71222,6 @@
       <c r="J1334" t="n">
         <v>4</v>
       </c>
-      <c r="K1334" t="inlineStr"/>
       <c r="L1334" t="inlineStr">
         <is>
           <t>1.5%</t>
@@ -71283,8 +71232,6 @@
           <t>565天</t>
         </is>
       </c>
-      <c r="N1334" t="inlineStr"/>
-      <c r="O1334" t="inlineStr"/>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
@@ -71327,7 +71274,6 @@
       <c r="J1335" t="n">
         <v>4</v>
       </c>
-      <c r="K1335" t="inlineStr"/>
       <c r="L1335" t="inlineStr">
         <is>
           <t>1.5%</t>
@@ -71338,8 +71284,6 @@
           <t>565天</t>
         </is>
       </c>
-      <c r="N1335" t="inlineStr"/>
-      <c r="O1335" t="inlineStr"/>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
@@ -71512,7 +71456,6 @@
       <c r="J1338" t="n">
         <v>0</v>
       </c>
-      <c r="K1338" t="inlineStr"/>
       <c r="L1338" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71523,8 +71466,6 @@
           <t>631天</t>
         </is>
       </c>
-      <c r="N1338" t="inlineStr"/>
-      <c r="O1338" t="inlineStr"/>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
@@ -71567,7 +71508,6 @@
       <c r="J1339" t="n">
         <v>0</v>
       </c>
-      <c r="K1339" t="inlineStr"/>
       <c r="L1339" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71578,8 +71518,6 @@
           <t>631天</t>
         </is>
       </c>
-      <c r="N1339" t="inlineStr"/>
-      <c r="O1339" t="inlineStr"/>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
@@ -71752,7 +71690,6 @@
       <c r="J1342" t="n">
         <v>0</v>
       </c>
-      <c r="K1342" t="inlineStr"/>
       <c r="L1342" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71763,8 +71700,6 @@
           <t>667天</t>
         </is>
       </c>
-      <c r="N1342" t="inlineStr"/>
-      <c r="O1342" t="inlineStr"/>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
@@ -71807,7 +71742,6 @@
       <c r="J1343" t="n">
         <v>0</v>
       </c>
-      <c r="K1343" t="inlineStr"/>
       <c r="L1343" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71818,8 +71752,6 @@
           <t>667天</t>
         </is>
       </c>
-      <c r="N1343" t="inlineStr"/>
-      <c r="O1343" t="inlineStr"/>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
@@ -71862,7 +71794,6 @@
       <c r="J1344" t="n">
         <v>0</v>
       </c>
-      <c r="K1344" t="inlineStr"/>
       <c r="L1344" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71873,8 +71804,6 @@
           <t>846天</t>
         </is>
       </c>
-      <c r="N1344" t="inlineStr"/>
-      <c r="O1344" t="inlineStr"/>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
@@ -71917,7 +71846,6 @@
       <c r="J1345" t="n">
         <v>0</v>
       </c>
-      <c r="K1345" t="inlineStr"/>
       <c r="L1345" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -71928,8 +71856,2284 @@
           <t>846天</t>
         </is>
       </c>
-      <c r="N1345" t="inlineStr"/>
-      <c r="O1345" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Beyond Gravity ˸ An Interplanetary Travel Showcase</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>wrld_660d90dd-2a8e-4743-9b70-1c6237f8192b</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>2026-04-07T18:06:24.145Z</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v>163</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1346" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1346" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>2.45%</t>
+        </is>
+      </c>
+      <c r="M1346" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Beyond Gravity ˸ An Interplanetary Travel Showcase</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>wrld_660d90dd-2a8e-4743-9b70-1c6237f8192b</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>2026-04-07T18:06:24.145Z</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v>163</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1347" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1347" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>2.45%</t>
+        </is>
+      </c>
+      <c r="M1347" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>SpeedStar Paradise （StarSight Mt․觀星山 CVS2）</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>wrld_c0f03f3e-ca4c-48cb-8aea-14ed13c1ee03</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>2025-11-17T14:03:16.240Z</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>2026-02-21T14:40:32.411Z</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v>1288</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>47</v>
+      </c>
+      <c r="I1348" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1348" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1348" t="inlineStr">
+        <is>
+          <t>4天</t>
+        </is>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="M1348" t="inlineStr">
+        <is>
+          <t>45天</t>
+        </is>
+      </c>
+      <c r="N1348" t="inlineStr">
+        <is>
+          <t>141天</t>
+        </is>
+      </c>
+      <c r="O1348" t="n">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>SpeedStar Paradise （StarSight Mt․觀星山 CVS2）</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>wrld_c0f03f3e-ca4c-48cb-8aea-14ed13c1ee03</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>2025-11-17T14:03:16.240Z</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>2026-02-21T14:40:32.411Z</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
+        <v>1288</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>47</v>
+      </c>
+      <c r="I1349" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1349" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1349" t="inlineStr">
+        <is>
+          <t>4天</t>
+        </is>
+      </c>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="M1349" t="inlineStr">
+        <is>
+          <t>45天</t>
+        </is>
+      </c>
+      <c r="N1349" t="inlineStr">
+        <is>
+          <t>141天</t>
+        </is>
+      </c>
+      <c r="O1349" t="n">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Project Origin v1․0 Hangout and chill ǃ （Minecraft Build Project）</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>wrld_fb9540f8-68f1-42e8-9430-558fc2d568c4</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>2023-10-15T12:21:09.717Z</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>2025-11-12T15:28:46.998Z</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v>4839</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>190</v>
+      </c>
+      <c r="I1350" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1350" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1350" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="M1350" t="inlineStr">
+        <is>
+          <t>146天</t>
+        </is>
+      </c>
+      <c r="N1350" t="inlineStr">
+        <is>
+          <t>905天</t>
+        </is>
+      </c>
+      <c r="O1350" t="n">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Project Origin v1․0 Hangout and chill ǃ （Minecraft Build Project）</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>wrld_fb9540f8-68f1-42e8-9430-558fc2d568c4</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>2023-10-15T12:21:09.717Z</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>2025-11-12T15:28:46.998Z</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v>4839</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>190</v>
+      </c>
+      <c r="I1351" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1351" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1351" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="M1351" t="inlineStr">
+        <is>
+          <t>146天</t>
+        </is>
+      </c>
+      <c r="N1351" t="inlineStr">
+        <is>
+          <t>905天</t>
+        </is>
+      </c>
+      <c r="O1351" t="n">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Starsight Museum</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>wrld_befc82b9-48d1-4d2a-8269-fb1ac1518f69</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>2025-08-13T13:48:58.458Z</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1352" t="inlineStr">
+        <is>
+          <t>237天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Starsight Museum</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>wrld_befc82b9-48d1-4d2a-8269-fb1ac1518f69</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>2025-08-13T13:48:58.458Z</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1353" t="inlineStr">
+        <is>
+          <t>237天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>wrld_44e2cf46-b090-4c70-b5ba-9f7e7ec89d4f</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>2025-08-09T16:53:49.952Z</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1354" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1354" t="inlineStr">
+        <is>
+          <t>241天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>wrld_44e2cf46-b090-4c70-b5ba-9f7e7ec89d4f</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>2025-08-09T16:53:49.952Z</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1355" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1355" t="inlineStr">
+        <is>
+          <t>241天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge CVS2 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>wrld_c4d985d3-11de-4a89-9e8b-60b0342a1676</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>2025-05-03T22:35:59.524Z</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>2025-08-02T09:39:48.354Z</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
+        <v>3601</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>144</v>
+      </c>
+      <c r="I1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1356" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1356" t="inlineStr">
+        <is>
+          <t>12天</t>
+        </is>
+      </c>
+      <c r="L1356" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="M1356" t="inlineStr">
+        <is>
+          <t>248天</t>
+        </is>
+      </c>
+      <c r="N1356" t="inlineStr">
+        <is>
+          <t>339天</t>
+        </is>
+      </c>
+      <c r="O1356" t="n">
+        <v>10.62</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge CVS2 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>wrld_c4d985d3-11de-4a89-9e8b-60b0342a1676</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>2025-05-03T22:35:59.524Z</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>2025-08-02T09:39:48.354Z</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v>3601</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>144</v>
+      </c>
+      <c r="I1357" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1357" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1357" t="inlineStr">
+        <is>
+          <t>12天</t>
+        </is>
+      </c>
+      <c r="L1357" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="M1357" t="inlineStr">
+        <is>
+          <t>248天</t>
+        </is>
+      </c>
+      <c r="N1357" t="inlineStr">
+        <is>
+          <t>339天</t>
+        </is>
+      </c>
+      <c r="O1357" t="n">
+        <v>10.62</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>StarRiver Space Program v0․1․1 LiftOff</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>wrld_f3acb654-f2ab-49aa-9108-d261c53c5d64</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>2025-07-13T11:38:02.242Z</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1358" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1358" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1358" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="M1358" t="inlineStr">
+        <is>
+          <t>268天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>StarRiver Space Program v0․1․1 LiftOff</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>wrld_f3acb654-f2ab-49aa-9108-d261c53c5d64</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>2025-07-13T11:38:02.242Z</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1359" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1359" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1359" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="M1359" t="inlineStr">
+        <is>
+          <t>268天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T SunMoonLake 日月潭 南投山道</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>wrld_1b189721-fa5d-4c64-a24b-9a2c5b89b3b5</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>2025-07-06T07:24:59.566Z</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1360" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1360" t="inlineStr">
+        <is>
+          <t>275天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T SunMoonLake 日月潭 南投山道</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>wrld_1b189721-fa5d-4c64-a24b-9a2c5b89b3b5</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>2025-07-06T07:24:59.566Z</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1361" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1361" t="inlineStr">
+        <is>
+          <t>275天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T WuLing 武嶺（佐久間峠） 合歡山山道</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>wrld_5fb84156-598a-43c8-8a2b-2c9aa7c95b40</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>2025-07-03T13:07:32.404Z</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1362" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1362" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="M1362" t="inlineStr">
+        <is>
+          <t>278天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T WuLing 武嶺（佐久間峠） 合歡山山道</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>wrld_5fb84156-598a-43c8-8a2b-2c9aa7c95b40</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>2025-07-03T13:07:32.404Z</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1363" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1363" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="M1363" t="inlineStr">
+        <is>
+          <t>278天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge Sacc 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>wrld_a6f9cdae-d393-4572-b019-015e4ec6eb35</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>2025-04-09T11:56:42.006Z</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>2025-05-27T15:40:33.056Z</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
+        <v>918</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>72</v>
+      </c>
+      <c r="I1364" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1364" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1364" t="inlineStr">
+        <is>
+          <t>15天</t>
+        </is>
+      </c>
+      <c r="L1364" t="inlineStr">
+        <is>
+          <t>7.84%</t>
+        </is>
+      </c>
+      <c r="M1364" t="inlineStr">
+        <is>
+          <t>315天</t>
+        </is>
+      </c>
+      <c r="N1364" t="inlineStr">
+        <is>
+          <t>363天</t>
+        </is>
+      </c>
+      <c r="O1364" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge Sacc 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>wrld_a6f9cdae-d393-4572-b019-015e4ec6eb35</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>2025-04-09T11:56:42.006Z</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>2025-05-27T15:40:33.056Z</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
+        <v>918</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>72</v>
+      </c>
+      <c r="I1365" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1365" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1365" t="inlineStr">
+        <is>
+          <t>15天</t>
+        </is>
+      </c>
+      <c r="L1365" t="inlineStr">
+        <is>
+          <t>7.84%</t>
+        </is>
+      </c>
+      <c r="M1365" t="inlineStr">
+        <is>
+          <t>315天</t>
+        </is>
+      </c>
+      <c r="N1365" t="inlineStr">
+        <is>
+          <t>363天</t>
+        </is>
+      </c>
+      <c r="O1365" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>日月潭外周道 Sun Moon Lake</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>wrld_6e465490-9b15-4d2b-b4fe-1ea06e09e55a</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>2025-05-17T13:55:05.489Z</t>
+        </is>
+      </c>
+      <c r="F1366" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1366" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1366" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1366" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="M1366" t="inlineStr">
+        <is>
+          <t>325天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>日月潭外周道 Sun Moon Lake</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>wrld_6e465490-9b15-4d2b-b4fe-1ea06e09e55a</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>2025-05-17T13:55:05.489Z</t>
+        </is>
+      </c>
+      <c r="F1367" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1367" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1367" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="M1367" t="inlineStr">
+        <is>
+          <t>325天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>星門廣場StarGATE Exhibition</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>wrld_16498412-b9e0-404c-9da7-114484c89ecd</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>2024-07-22T05:06:07.749Z</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>2025-05-08T16:46:38.069Z</t>
+        </is>
+      </c>
+      <c r="F1368" t="n">
+        <v>826</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1368" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1368" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1368" t="inlineStr">
+        <is>
+          <t>24天</t>
+        </is>
+      </c>
+      <c r="L1368" t="inlineStr">
+        <is>
+          <t>2.18%</t>
+        </is>
+      </c>
+      <c r="M1368" t="inlineStr">
+        <is>
+          <t>334天</t>
+        </is>
+      </c>
+      <c r="N1368" t="inlineStr">
+        <is>
+          <t>624天</t>
+        </is>
+      </c>
+      <c r="O1368" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>星門廣場StarGATE Exhibition</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>wrld_16498412-b9e0-404c-9da7-114484c89ecd</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>2024-07-22T05:06:07.749Z</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>2025-05-08T16:46:38.069Z</t>
+        </is>
+      </c>
+      <c r="F1369" t="n">
+        <v>826</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1369" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1369" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1369" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1369" t="inlineStr">
+        <is>
+          <t>24天</t>
+        </is>
+      </c>
+      <c r="L1369" t="inlineStr">
+        <is>
+          <t>2.18%</t>
+        </is>
+      </c>
+      <c r="M1369" t="inlineStr">
+        <is>
+          <t>334天</t>
+        </is>
+      </c>
+      <c r="N1369" t="inlineStr">
+        <is>
+          <t>624天</t>
+        </is>
+      </c>
+      <c r="O1369" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Iseri Nina's Room （Girls Band Cry）</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>wrld_014b19d4-10fc-448d-aaf4-100067cc8eb2</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>2025-12-15T07:34:25.776Z</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>2025-04-10T13:03:37.715Z</t>
+        </is>
+      </c>
+      <c r="F1370" t="n">
+        <v>520</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1370" t="n">
+        <v>70</v>
+      </c>
+      <c r="I1370" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1370" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1370" t="inlineStr">
+        <is>
+          <t>258天</t>
+        </is>
+      </c>
+      <c r="L1370" t="inlineStr">
+        <is>
+          <t>13.46%</t>
+        </is>
+      </c>
+      <c r="M1370" t="inlineStr">
+        <is>
+          <t>362天</t>
+        </is>
+      </c>
+      <c r="N1370" t="inlineStr">
+        <is>
+          <t>113天</t>
+        </is>
+      </c>
+      <c r="O1370" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Iseri Nina's Room （Girls Band Cry）</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>wrld_014b19d4-10fc-448d-aaf4-100067cc8eb2</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>2025-12-15T07:34:25.776Z</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>2025-04-10T13:03:37.715Z</t>
+        </is>
+      </c>
+      <c r="F1371" t="n">
+        <v>520</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1371" t="n">
+        <v>70</v>
+      </c>
+      <c r="I1371" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1371" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1371" t="inlineStr">
+        <is>
+          <t>258天</t>
+        </is>
+      </c>
+      <c r="L1371" t="inlineStr">
+        <is>
+          <t>13.46%</t>
+        </is>
+      </c>
+      <c r="M1371" t="inlineStr">
+        <is>
+          <t>362天</t>
+        </is>
+      </c>
+      <c r="N1371" t="inlineStr">
+        <is>
+          <t>113天</t>
+        </is>
+      </c>
+      <c r="O1371" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Metro Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>wrld_39eab7ef-be49-4bb2-bb63-56bc30200b82</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>2024-11-24T13:59:30.261Z</t>
+        </is>
+      </c>
+      <c r="F1372" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1372" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1372" t="inlineStr">
+        <is>
+          <t>499天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Metro Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>wrld_39eab7ef-be49-4bb2-bb63-56bc30200b82</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>2024-11-24T13:59:30.261Z</t>
+        </is>
+      </c>
+      <c r="F1373" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1373" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1373" t="inlineStr">
+        <is>
+          <t>499天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Taipei MRT 大坪林站 by StarRiver（未完成）</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>wrld_b7193f7d-4616-4b3e-8236-e2f4c7da2d8d</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>2024-09-15T05:18:23.226Z</t>
+        </is>
+      </c>
+      <c r="F1374" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1374" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1374" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1374" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="M1374" t="inlineStr">
+        <is>
+          <t>569天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Taipei MRT 大坪林站 by StarRiver（未完成）</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>wrld_b7193f7d-4616-4b3e-8236-e2f4c7da2d8d</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>2024-09-15T05:18:23.226Z</t>
+        </is>
+      </c>
+      <c r="F1375" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1375" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1375" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1375" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="M1375" t="inlineStr">
+        <is>
+          <t>569天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Free Trajectory -A Landscape Recreation Experience</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>wrld_81e98a0f-b8eb-4a9b-b01b-35d26758c41c</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>2024-07-23T14:43:36.014Z</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>2024-07-22T19:52:03.599Z</t>
+        </is>
+      </c>
+      <c r="F1376" t="n">
+        <v>373</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1376" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1376" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1376" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="L1376" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="M1376" t="inlineStr">
+        <is>
+          <t>624天</t>
+        </is>
+      </c>
+      <c r="N1376" t="inlineStr">
+        <is>
+          <t>623天</t>
+        </is>
+      </c>
+      <c r="O1376" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Free Trajectory -A Landscape Recreation Experience</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>wrld_81e98a0f-b8eb-4a9b-b01b-35d26758c41c</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>2024-07-23T14:43:36.014Z</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>2024-07-22T19:52:03.599Z</t>
+        </is>
+      </c>
+      <c r="F1377" t="n">
+        <v>373</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1377" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1377" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1377" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="L1377" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="M1377" t="inlineStr">
+        <is>
+          <t>624天</t>
+        </is>
+      </c>
+      <c r="N1377" t="inlineStr">
+        <is>
+          <t>623天</t>
+        </is>
+      </c>
+      <c r="O1377" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Project：Hide＆Seek LAB（UNFINISHED ）</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>wrld_bac386e9-a543-48e7-a12d-fe9bd3521493</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>2024-07-11T09:44:06.067Z</t>
+        </is>
+      </c>
+      <c r="F1378" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1378" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1378" t="inlineStr">
+        <is>
+          <t>635天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Project：Hide＆Seek LAB（UNFINISHED ）</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>wrld_bac386e9-a543-48e7-a12d-fe9bd3521493</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>2024-07-11T09:44:06.067Z</t>
+        </is>
+      </c>
+      <c r="F1379" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1379" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1379" t="inlineStr">
+        <is>
+          <t>635天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Simple Green Room（Quest 3 MR）</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>wrld_14e668e2-f41b-4655-9440-51be3be0ae81</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>2024-07-08T21:05:28.545Z</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>2024-07-11T08:38:23.384Z</t>
+        </is>
+      </c>
+      <c r="F1380" t="n">
+        <v>1055</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1380" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1380" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1380" t="inlineStr">
+        <is>
+          <t>263天</t>
+        </is>
+      </c>
+      <c r="L1380" t="inlineStr">
+        <is>
+          <t>4.93%</t>
+        </is>
+      </c>
+      <c r="M1380" t="inlineStr">
+        <is>
+          <t>635天</t>
+        </is>
+      </c>
+      <c r="N1380" t="inlineStr">
+        <is>
+          <t>638天</t>
+        </is>
+      </c>
+      <c r="O1380" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Simple Green Room（Quest 3 MR）</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>wrld_14e668e2-f41b-4655-9440-51be3be0ae81</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>2024-07-08T21:05:28.545Z</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>2024-07-11T08:38:23.384Z</t>
+        </is>
+      </c>
+      <c r="F1381" t="n">
+        <v>1055</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1381" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1381" t="inlineStr">
+        <is>
+          <t>263天</t>
+        </is>
+      </c>
+      <c r="L1381" t="inlineStr">
+        <is>
+          <t>4.93%</t>
+        </is>
+      </c>
+      <c r="M1381" t="inlineStr">
+        <is>
+          <t>635天</t>
+        </is>
+      </c>
+      <c r="N1381" t="inlineStr">
+        <is>
+          <t>638天</t>
+        </is>
+      </c>
+      <c r="O1381" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Ruined斷垣殘壁 （測試）</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>wrld_7d7a9a66-df6a-4e2c-96fb-19b4dc53c430</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>2024-06-04T16:33:51.575Z</t>
+        </is>
+      </c>
+      <c r="F1382" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1382" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1382" t="inlineStr">
+        <is>
+          <t>672天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Ruined斷垣殘壁 （測試）</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>wrld_7d7a9a66-df6a-4e2c-96fb-19b4dc53c430</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>2024-06-04T16:33:51.575Z</t>
+        </is>
+      </c>
+      <c r="F1383" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1383" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1383" t="inlineStr">
+        <is>
+          <t>672天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Project˸ Taiwan</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>wrld_2e5e73d8-758f-4e2d-87db-7770762d52f0</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>2023-12-08T22:31:41.588Z</t>
+        </is>
+      </c>
+      <c r="F1384" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1384" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1384" t="inlineStr">
+        <is>
+          <t>851天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Project˸ Taiwan</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>wrld_2e5e73d8-758f-4e2d-87db-7770762d52f0</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>2023-12-08T22:31:41.588Z</t>
+        </is>
+      </c>
+      <c r="F1385" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1385" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1385" t="inlineStr">
+        <is>
+          <t>851天</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O655">
